--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-13_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-13_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +469,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5x5 Indoor Good 3rd floor</t>
+          <t>5x5 Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -480,55 +481,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10x5 DriveUp Original Units</t>
+          <t>5x5 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>139.00</t>
+          <t>95.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5x10 DriveUp Original Units</t>
+          <t>10x5 DriveUp Original Units</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>143.00</t>
+          <t>139.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5x10 Driveup Hallway</t>
+          <t>5x10 DriveUp Original Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>149.00</t>
+          <t>143.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10x5 Indoor Best 2nd floor</t>
+          <t>5x10 Driveup Hallway</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>153.00</t>
+          <t>145.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x5 Indoor Good 2nd floor</t>
+          <t>10x5 Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -540,31 +541,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5x10 Indoor Good 3rd floor</t>
+          <t>10x5 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>153.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 3rd floor</t>
+          <t>5x10 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 3rd floor</t>
+          <t>10x20 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -576,19 +577,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 3rd floor</t>
+          <t>10x21 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>173.00</t>
+          <t>170.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 3rd floor</t>
+          <t>10x20 Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -600,31 +601,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8x9 Bins Self Storage</t>
+          <t>10x21 Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>174.00</t>
+          <t>173.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15x5 Indoor Good 2nd floor</t>
+          <t>8x9 Bins Self Storage</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>174.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 3rd floor</t>
+          <t>15x5 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -636,31 +637,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5x15 Indoor Better 3rd floor</t>
+          <t>10x20 Indoor Best 3rd floor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>178.00</t>
+          <t>175.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 2nd floor</t>
+          <t>5x15 DriveUp Original Units</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>181.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 3rd floor</t>
+          <t>10x10 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -672,7 +673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 2nd floor</t>
+          <t>10x10 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -684,7 +685,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 3rd floor</t>
+          <t>10x11 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -696,19 +697,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 2nd floor</t>
+          <t>10x11 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>212.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 3rd floor</t>
+          <t>10x10 Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -720,7 +721,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10x11 Indoor Better 2nd floor</t>
+          <t>10x10 Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -732,31 +733,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10x10 DriveUp Original Units</t>
+          <t>10x11 Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>217.00</t>
+          <t>215.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 2nd floor</t>
+          <t>10x10 Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>220.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 3rd floor</t>
+          <t>10x15 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -768,55 +769,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 1st floor</t>
+          <t>10x15 Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10x16 Indoor Good 1st floor</t>
+          <t>10x15 Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>309.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x16 Indoor Better 1st floor</t>
+          <t>10x16 Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>320.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 2nd floor</t>
+          <t>10x16 Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>328.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 2nd floor</t>
+          <t>10x20 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -828,19 +829,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 2nd floor</t>
+          <t>10x21 Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>340.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 2nd floor</t>
+          <t>10x20 Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -852,19 +853,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 2nd floor</t>
+          <t>10x21 Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>345.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x21 Indoor Best 2nd floor</t>
+          <t>10x20 Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -876,19 +877,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 1st floor</t>
+          <t>10x21 Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>350.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13.5x18.5 1201 Bldg</t>
+          <t>10x20 Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -900,34 +901,58 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 1st floor</t>
+          <t>13.5x18.5 1201 Bldg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10x25 Driveup New</t>
+          <t>10x20 Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>599.00</t>
+          <t>420.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>10x30 DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>555.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10x25 Driveup New</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>599.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>10x30 Driveup New</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>749.00</t>
         </is>
@@ -944,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,96 +1059,96 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 x 13</t>
+          <t>10 x 10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$233</t>
+          <t>$239</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10 x 15</t>
+          <t>8 x 15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$259</t>
+          <t>$273</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10 x 15</t>
+          <t>10 x 13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$319</t>
+          <t>$233</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9 x 18</t>
+          <t>10 x 15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$376</t>
+          <t>$259</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10 x 17</t>
+          <t>10 x 15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$384</t>
+          <t>$319</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9 x 19</t>
+          <t>9 x 18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$389</t>
+          <t>$376</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 x 18</t>
+          <t>10 x 17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$386</t>
+          <t>$384</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10 x 18</t>
+          <t>9 x 19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$410</t>
+          <t>$389</t>
         </is>
       </c>
     </row>
@@ -1135,43 +1160,669 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$467</t>
+          <t>$386</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10 x 20</t>
+          <t>10 x 18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$429</t>
+          <t>$410</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 x 20</t>
+          <t>10 x 18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$514</t>
+          <t>$467</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11 x 20</t>
+          <t>10 x 20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$272</t>
+          <t>$429</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10 x 20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$514</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5'X5'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$114.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5'X10'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$164.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5'X15'X8' (Indoor, Heated, First Floor Access)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$204.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8'X10'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$224.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10'X8'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$246.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5'X4'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5'X5'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5'X8'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5'X10'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5'X10'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10'X10'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$269.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10'X15'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$375.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10'X14'X8' (Heated, Drive-Up)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10'X11'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10'X20'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$449.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10'X25'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$629.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10'X30'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$825.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20'X20'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$1101.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20'X25'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$1132.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30'X20'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11'X19'X8' (Drive-Up, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10'X32'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15'X20'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10'X40'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15'X30'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15'X40'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20'X30'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>40'X20'X8' (Drive-Up, Non-Climate Control)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8'X18' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>$159.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8'X23' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>$169.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8'X28' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$179.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8'X23' (Seasonal, Paved)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>$184.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8'X33' (Seasonal, Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>$199.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8'X38' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>$229.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8'X33' (Seasonal, Paved)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>$244.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10'X28' (Paved)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>$259.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8'X38' (Seasonal, Paved)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>$259.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10'X23' (Paved)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8'X17' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8'X21' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10'X18' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10'X33' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10'X23' (Seasonal, Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8'X18' (Paved)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8'X28' (Paved)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8'X31' (Non-Paved)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10'X38' (Seasonal, Paved)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1829,4 +1831,656 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard (5 x 5 x 4)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$79</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Standard (5 x 5)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5X5CC (5 x 5 x 8)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$117</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Standard (5 x 10)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$175</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5X10CC (5 x 10)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$190</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10X10CC (10 x 10)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$270</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Standard (10 x 15)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$375</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Standard (10 x 20)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>$450</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Heated 10X20CC (10 x 20)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Standard (10 x 25)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$575</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Standard (10 x 30)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$695</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Standard (15 x 30)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$760</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Standard (20 x 20)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$750</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Paved Outside Parking (19 x 9)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$199</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$299</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ultimate  (10 x 20 x 10)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$579</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 30 (10 x 30 x 10)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$650</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 40 (10 x 40 x 10)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$1,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ultimate 20 x 40 (20 x 40 x 10)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$1,737</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$299</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 20 (10 x 20 x 10)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$579</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ultimate 10 x 30 (30 x 10)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$650</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ultimate 20 x 20  (20 x 20 x 10)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$725</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10X20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$365.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$199.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$199.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$260.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$240.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$305.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$365.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10x25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>$405.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$475.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>$450.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12x20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>$385.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12x20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>$440.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12x30 (CC)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>$570.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12x35</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>$470.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13x25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>$440.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15x20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>$440.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15x25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>$530.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3X2.7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5X4X4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5X5X4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>$85.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5X5X8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>$90.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>$165.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>$175.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>$175.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7x25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>$260.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Outdoor Parking</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>$110.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Outdoor Parking</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>$145.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,16 +429,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -447,10 +452,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5x5 Driveup Hallway</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>Driveup Hallway</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>89.00</t>
         </is>
@@ -459,10 +469,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5x5 Indoor Better 2nd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -471,10 +486,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5x5 Indoor Better 3rd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -483,10 +503,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5x5 Indoor Good 3rd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -495,10 +520,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10x5 DriveUp Original Units</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>139.00</t>
         </is>
@@ -507,10 +537,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5x10 DriveUp Original Units</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>143.00</t>
         </is>
@@ -519,10 +554,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5x10 Driveup Hallway</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Driveup Hallway</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>145.00</t>
         </is>
@@ -531,10 +571,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x5 Indoor Best 2nd floor</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>153.00</t>
         </is>
@@ -543,10 +588,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10x5 Indoor Good 2nd floor</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>153.00</t>
         </is>
@@ -555,10 +605,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5x10 Indoor Good 3rd floor</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>159.00</t>
         </is>
@@ -567,10 +622,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>170.00</t>
         </is>
@@ -579,10 +639,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 3rd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>170.00</t>
         </is>
@@ -591,10 +656,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>173.00</t>
         </is>
@@ -603,10 +673,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 3rd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>173.00</t>
         </is>
@@ -615,10 +690,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8x9 Bins Self Storage</t>
+          <t>8x9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
+        <is>
+          <t>Bins Self Storage</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>174.00</t>
         </is>
@@ -627,10 +707,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15x5 Indoor Good 2nd floor</t>
+          <t>15x5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
@@ -639,10 +724,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
+        <is>
+          <t>Indoor Best 3rd floor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
@@ -651,10 +741,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5x15 DriveUp Original Units</t>
+          <t>5x15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>181.00</t>
         </is>
@@ -663,10 +758,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 2nd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -675,10 +775,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 3rd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -687,10 +792,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 2nd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -699,10 +809,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 3rd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -711,10 +826,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 2nd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -723,10 +843,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 3rd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -735,10 +860,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10x11 Indoor Better 2nd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -747,10 +877,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 1st floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>220.00</t>
         </is>
@@ -759,10 +894,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 2nd floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>270.00</t>
         </is>
@@ -771,10 +911,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 3rd floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>270.00</t>
         </is>
@@ -783,10 +928,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 1st floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>309.00</t>
         </is>
@@ -795,10 +945,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x16 Indoor Good 1st floor</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>320.00</t>
         </is>
@@ -807,10 +962,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10x16 Indoor Better 1st floor</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
+        <is>
+          <t>Indoor Better 1st floor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>328.00</t>
         </is>
@@ -819,10 +979,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>340.00</t>
         </is>
@@ -831,10 +996,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>340.00</t>
         </is>
@@ -843,10 +1013,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>345.00</t>
         </is>
@@ -855,10 +1030,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>345.00</t>
         </is>
@@ -867,10 +1047,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
@@ -879,10 +1064,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x21 Indoor Best 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
@@ -891,10 +1081,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 1st floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
+        <is>
+          <t>Indoor Better 1st floor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>410.00</t>
         </is>
@@ -903,10 +1098,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13.5x18.5 1201 Bldg</t>
+          <t>13.5x18.5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
+        <is>
+          <t>1201 Bldg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>410.00</t>
         </is>
@@ -915,10 +1115,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 1st floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Indoor Best 1st floor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>420.00</t>
         </is>
@@ -927,10 +1132,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10x30 DriveUp Original Units</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>555.00</t>
         </is>
@@ -939,10 +1149,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10x25 Driveup New</t>
+          <t>10x25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>599.00</t>
         </is>
@@ -951,10 +1166,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10x30 Driveup New</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>749.00</t>
         </is>
@@ -971,16 +1191,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -989,228 +1214,234 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5 x 5</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>$88</t>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>88.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5 x 5</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$101</t>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>101.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5 x 10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$181</t>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>181.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 x 10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$190</t>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9 x 11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$293</t>
+          <t>9x11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>293.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 x 10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$228</t>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>228.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 x 10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$239</t>
+          <t>8x15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>273.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8 x 15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>$273</t>
+          <t>10x13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>233.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10 x 13</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>$233</t>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 x 15</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$259</t>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>319.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10 x 15</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>$319</t>
+          <t>9x18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>376.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9 x 18</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>$376</t>
+          <t>10x17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>384.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 x 17</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>$384</t>
+          <t>9x19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>389.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9 x 19</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>$389</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>386.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>$386</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>$410</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>467.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>$467</t>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>429.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 x 20</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$429</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10 x 20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>$514</t>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>514.00</t>
         </is>
       </c>
     </row>
@@ -1225,16 +1456,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -1243,70 +1479,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$114.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>114.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$164.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>164.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5'X15'X8' (Indoor, Heated, First Floor Access)</t>
+          <t>5X15X8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$204.00</t>
+          <t>Indoor Heated First Floor Access</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>204.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>8X10X8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$224.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>224.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10'X8'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X8X8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$246.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>246.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>4X5X8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1315,10 +1581,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1327,10 +1598,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5'X4'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X4X8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1339,10 +1615,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1351,10 +1632,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5'X8'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X8X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1363,10 +1649,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1375,10 +1666,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1387,34 +1683,49 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X10X8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$269.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>269.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10'X15'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X15X8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$375.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>375.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10'X14'X8' (Heated, Drive-Up)</t>
+          <t>10X14X8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
+        <is>
+          <t>Heated Drive-Up</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1423,10 +1734,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10'X11'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>10X11X8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1435,70 +1751,100 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X20X8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$449.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>449.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10'X25'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X25X8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$629.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>629.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X30X8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$825.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>825.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X20X8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$1101.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1101.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20'X25'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X25X8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$1132.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1132.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>30X20X8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1507,10 +1853,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11'X19'X8' (Drive-Up, A/C &amp; Heat)</t>
+          <t>11X19X8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>Drive-Up A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1519,10 +1870,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10'X32'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X32X8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1531,10 +1887,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15'X20'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>15X20X8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1543,10 +1904,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10'X40'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X40X8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1555,10 +1921,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>15X30X8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1567,10 +1938,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15'X40'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>15X40X8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1579,10 +1955,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X30X8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1591,10 +1972,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>40X20X8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1603,118 +1989,168 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8'X18' (Non-Paved)</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8'X23' (Non-Paved)</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>169.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8'X28' (Non-Paved)</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>179.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8'X23' (Seasonal, Paved)</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$184.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>184.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8'X33' (Seasonal, Non-Paved)</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>$199.00</t>
+          <t>Seasonal Non-Paved</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8'X38' (Non-Paved)</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>229.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8'X33' (Seasonal, Paved)</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>$244.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>244.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10'X28' (Paved)</t>
+          <t>10X28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>$259.00</t>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8'X38' (Seasonal, Paved)</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>$259.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10'X23' (Paved)</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1723,10 +2159,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8'X17' (Non-Paved)</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1735,10 +2176,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8'X21' (Non-Paved)</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1747,10 +2193,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10'X18' (Non-Paved)</t>
+          <t>10X18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1759,10 +2210,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10'X33' (Non-Paved)</t>
+          <t>10X33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1771,10 +2227,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10'X23' (Seasonal, Non-Paved)</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
+        <is>
+          <t>Seasonal Non-Paved</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1783,10 +2244,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8'X18' (Paved)</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1795,10 +2261,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8'X28' (Paved)</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1807,10 +2278,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8'X31' (Non-Paved)</t>
+          <t>8X31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1819,10 +2295,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10'X38' (Seasonal, Paved)</t>
+          <t>10X38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
+        <is>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1839,16 +2320,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -1857,276 +2343,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Standard (5 x 5 x 4)</t>
+          <t>5x5x4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$79</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Standard (5 x 5)</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$99</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>99.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5X5CC (5 x 5 x 8)</t>
+          <t>5x5x8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$117</t>
+          <t>5X5CC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>117.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Standard (5 x 10)</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$175</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5X10CC (5 x 10)</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$190</t>
+          <t>5X10CC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10X10CC (10 x 10)</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$270</t>
+          <t>10X10CC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Standard (10 x 15)</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$375</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>375.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Standard (10 x 20)</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$450</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>450.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Heated 10X20CC (10 x 20)</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>Heated 10X20CC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>500.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Standard (10 x 25)</t>
+          <t>10x25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$575</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>575.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Standard (10 x 30)</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$695</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>695.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Standard (15 x 30)</t>
+          <t>15x30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$760</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>760.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Standard (20 x 20)</t>
+          <t>20x20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$750</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>750.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paved Outside Parking (19 x 9)</t>
+          <t>19x9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$199</t>
+          <t>Paved Outside Parking</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+          <t>10x10x10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$299</t>
+          <t>Ultimate 10 x 10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>299.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ultimate  (10 x 20 x 10)</t>
+          <t>10x20x10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$579</t>
+          <t xml:space="preserve">Ultimate </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>579.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 30 (10 x 30 x 10)</t>
+          <t>10x30x10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$650</t>
+          <t>Ultimate 10 x 30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>650.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 40 (10 x 40 x 10)</t>
+          <t>10x40x10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$1,300</t>
+          <t>Ultimate 10 x 40</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1,300.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ultimate 20 x 40 (20 x 40 x 10)</t>
+          <t>20x40x10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$1,737</t>
+          <t>Ultimate 20 x 40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1,737.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+          <t>10x10x10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$299</t>
+          <t>Ultimate 10 x 10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>299.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 20 (10 x 20 x 10)</t>
+          <t>10x20x10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$579</t>
+          <t>Ultimate 10 x 20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>579.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 30 (30 x 10)</t>
+          <t>30x10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$650</t>
+          <t>Ultimate 10 x 30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>650.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ultimate 20 x 20  (20 x 20 x 10)</t>
+          <t>20x20x10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$725</t>
+          <t xml:space="preserve">Ultimate 20 x 20 </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>725.00</t>
         </is>
       </c>
     </row>
@@ -2141,16 +2742,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -2162,9 +2768,10 @@
           <t>10X20</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>$365.00</t>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>365.00</t>
         </is>
       </c>
     </row>
@@ -2174,9 +2781,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$199.00</t>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
@@ -2186,9 +2794,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$199.00</t>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
@@ -2198,9 +2807,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$260.00</t>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>260.00</t>
         </is>
       </c>
     </row>
@@ -2210,9 +2820,10 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$240.00</t>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>240.00</t>
         </is>
       </c>
     </row>
@@ -2222,9 +2833,10 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$305.00</t>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>305.00</t>
         </is>
       </c>
     </row>
@@ -2234,9 +2846,10 @@
           <t>10x20</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$365.00</t>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>365.00</t>
         </is>
       </c>
     </row>
@@ -2246,9 +2859,10 @@
           <t>10x25</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>$405.00</t>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>405.00</t>
         </is>
       </c>
     </row>
@@ -2258,9 +2872,10 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>$475.00</t>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>475.00</t>
         </is>
       </c>
     </row>
@@ -2270,9 +2885,10 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$450.00</t>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>450.00</t>
         </is>
       </c>
     </row>
@@ -2282,9 +2898,10 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>$385.00</t>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>385.00</t>
         </is>
       </c>
     </row>
@@ -2294,21 +2911,27 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12x30 (CC)</t>
+          <t>12x30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$570.00</t>
+          <t>(CC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>570.00</t>
         </is>
       </c>
     </row>
@@ -2318,9 +2941,10 @@
           <t>12x35</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>$470.00</t>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>470.00</t>
         </is>
       </c>
     </row>
@@ -2330,9 +2954,10 @@
           <t>13x25</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
@@ -2342,9 +2967,10 @@
           <t>15x20</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
@@ -2354,9 +2980,10 @@
           <t>15x25</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>$530.00</t>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>530.00</t>
         </is>
       </c>
     </row>
@@ -2366,9 +2993,10 @@
           <t>3X2.7</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$50.00</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>50.00</t>
         </is>
       </c>
     </row>
@@ -2378,9 +3006,10 @@
           <t>5X4X4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>$80.00</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>80.00</t>
         </is>
       </c>
     </row>
@@ -2390,9 +3019,10 @@
           <t>5X5X4</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>$85.00</t>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>85.00</t>
         </is>
       </c>
     </row>
@@ -2402,9 +3032,10 @@
           <t>5X5X8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>$90.00</t>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>90.00</t>
         </is>
       </c>
     </row>
@@ -2414,9 +3045,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>$165.00</t>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>165.00</t>
         </is>
       </c>
     </row>
@@ -2426,9 +3058,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>$175.00</t>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
@@ -2438,9 +3071,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>$175.00</t>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
@@ -2450,33 +3084,44 @@
           <t>7x25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>$260.00</t>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>260.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Outdoor Parking</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>110.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Outdoor Parking</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>145.00</t>
         </is>
       </c>
     </row>

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>89.00</t>
+          <t>85.00</t>
         </is>
       </c>
     </row>
@@ -474,12 +474,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>87.00</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indoor Better 3rd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -520,24 +520,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10x5</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>139.00</t>
+          <t>95.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>143.00</t>
+          <t>139.00</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>181.00</t>
+          <t>176.00</t>
         </is>
       </c>
     </row>
@@ -882,29 +882,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>217.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>220.00</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -933,19 +933,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>309.00</t>
         </is>
       </c>
     </row>
@@ -967,36 +967,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>320.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>338.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1013,24 +1013,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>340.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1047,24 +1047,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indoor Best 2nd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>345.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1081,29 +1081,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>350.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13.5x18.5</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1201 Bldg</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1115,34 +1115,34 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>13.5x18.5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indoor Best 1st floor</t>
+          <t>1201 Bldg</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>555.00</t>
+          <t>420.00</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,7 +1217,11 @@
           <t>5x5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>88.00</t>
@@ -1230,7 +1234,11 @@
           <t>5x5</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1st FloorClimate Controlled</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>101.00</t>
@@ -1243,7 +1251,11 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>181.00</t>
@@ -1256,7 +1268,11 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1st FloorClimate Controlled</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>190.00</t>
@@ -1269,7 +1285,11 @@
           <t>9x11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>293.00</t>
@@ -1282,7 +1302,11 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>228.00</t>
@@ -1295,7 +1319,11 @@
           <t>8x15</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1st FloorClimate Controlled</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>273.00</t>
@@ -1308,7 +1336,11 @@
           <t>10x13</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>233.00</t>
@@ -1321,7 +1353,11 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>259.00</t>
@@ -1334,7 +1370,11 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1st FloorClimate Controlled</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>319.00</t>
@@ -1347,7 +1387,11 @@
           <t>9x18</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elevator AccessPremiumClimate Controlled</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>376.00</t>
@@ -1360,7 +1404,11 @@
           <t>10x17</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Drive Up Access</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>384.00</t>
@@ -1373,7 +1421,11 @@
           <t>9x19</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>389.00</t>
@@ -1383,13 +1435,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10x18</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>9x19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Drive Up Access</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>386.00</t>
+          <t>449.00</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1455,14 @@
           <t>10x18</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>386.00</t>
         </is>
       </c>
     </row>
@@ -1412,23 +1472,31 @@
           <t>10x18</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1st FloorClimate Controlled</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>467.00</t>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x20</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Drive Up Access</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>429.00</t>
+          <t>467.00</t>
         </is>
       </c>
     </row>
@@ -1438,8 +1506,29 @@
           <t>10x20</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
+        <is>
+          <t>429.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Drive Up Access</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>514.00</t>
         </is>
@@ -1489,7 +1578,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>114.00</t>
+          <t>104.00</t>
         </is>
       </c>
     </row>
@@ -1506,31 +1595,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>164.00</t>
+          <t>174.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5X15X8</t>
+          <t>8X10X8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access</t>
+          <t>Drive-Up Non-Climate Control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>204.00</t>
+          <t>234.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8X10X8</t>
+          <t>10X8X8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1540,31 +1629,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>224.00</t>
+          <t>257.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10X8X8</t>
+          <t>4X5X8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Drive-Up Non-Climate Control</t>
+          <t>Indoor First Floor Access Non-Climate Control</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>246.00</t>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4X5X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1581,12 +1670,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>5X4X8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access Non-Climate Control</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1598,12 +1687,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5X4X8</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access Non-Climate Control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1632,12 +1721,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5X8X8</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1649,12 +1738,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5X10X8</t>
+          <t>5X15X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access Non-Climate Control</t>
+          <t>Indoor Heated First Floor Access</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1666,12 +1755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5X10X8</t>
+          <t>5X8X8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1693,7 +1782,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>269.00</t>
+          <t>259.00</t>
         </is>
       </c>
     </row>
@@ -1710,19 +1799,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>375.00</t>
+          <t>364.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10X14X8</t>
+          <t>10X11X8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heated Drive-Up</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1734,12 +1823,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10X11X8</t>
+          <t>10X14X8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Heated Drive-Up</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1795,7 +1884,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>825.00</t>
+          <t>902.00</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1901,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1101.00</t>
+          <t>1019.00</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2078,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8X18</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1999,14 +2088,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>169.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2016,41 +2105,41 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>169.00</t>
+          <t>179.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Non-Paved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>184.00</t>
+          <t>229.00</t>
         </is>
       </c>
     </row>
@@ -2062,92 +2151,92 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Seasonal Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>244.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>10X28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8X33</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>244.00</t>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10X28</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2159,7 +2248,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8X17</t>
+          <t>10X18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2176,7 +2265,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8X21</t>
+          <t>10X33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2193,12 +2282,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10X18</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2210,12 +2299,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10X33</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Non-Paved</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2227,12 +2316,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Seasonal Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2244,7 +2333,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8X18</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2261,12 +2350,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2278,12 +2367,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8X31</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2768,7 +2857,11 @@
           <t>10X20</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Double Unit/ Drive up access</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>365.00</t>
@@ -2781,7 +2874,11 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Non Climate Control- Indoor Access</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>199.00</t>
@@ -2794,7 +2891,11 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>199.00</t>
@@ -2807,7 +2908,11 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Climate Control- Indoor access</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>260.00</t>
@@ -2820,7 +2925,11 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>240.00</t>
@@ -2833,7 +2942,11 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Climate Control - Indoor access</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>305.00</t>
@@ -2846,7 +2959,11 @@
           <t>10x20</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>365.00</t>
@@ -2859,7 +2976,11 @@
           <t>10x25</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>405.00</t>
@@ -2872,7 +2993,11 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>475.00</t>
@@ -2885,7 +3010,11 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Climate Control</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>450.00</t>
@@ -2898,7 +3027,11 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>385.00</t>
@@ -2911,7 +3044,11 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Climate Control</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>440.00</t>
@@ -2941,7 +3078,11 @@
           <t>12x35</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>470.00</t>
@@ -2954,7 +3095,11 @@
           <t>13x25</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>440.00</t>
@@ -2967,7 +3112,11 @@
           <t>15x20</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>440.00</t>
@@ -2980,7 +3129,11 @@
           <t>15x25</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>530.00</t>
@@ -2993,7 +3146,11 @@
           <t>3X2.7</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>None listed</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>50.00</t>
@@ -3006,7 +3163,11 @@
           <t>5X4X4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Indoor Lockers</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>80.00</t>
@@ -3019,7 +3180,11 @@
           <t>5X5X4</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Indoor Lockers</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>85.00</t>
@@ -3032,7 +3197,11 @@
           <t>5X5X8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Indoor Lockers</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>90.00</t>
@@ -3045,7 +3214,11 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>165.00</t>
@@ -3058,7 +3231,11 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Climate Control- Indoor Access</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>175.00</t>
@@ -3071,7 +3248,11 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>175.00</t>
@@ -3084,7 +3265,11 @@
           <t>7x25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Drive up access</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>260.00</t>

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-26_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -554,17 +555,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Driveup Hallway</t>
+          <t>Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>145.00</t>
+          <t>153.00</t>
         </is>
       </c>
     </row>
@@ -576,7 +577,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indoor Best 2nd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -588,24 +589,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10x5</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>153.00</t>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -615,14 +616,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>170.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -639,17 +640,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>8x9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Bins Self Storage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>171.00</t>
         </is>
       </c>
     </row>
@@ -690,29 +691,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8x9</t>
+          <t>15x5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bins Self Storage</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>174.00</t>
+          <t>175.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15x5</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Best 3rd floor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -724,34 +725,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>5x15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Indoor Best 3rd floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>176.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>212.00</t>
         </is>
       </c>
     </row>
@@ -763,7 +764,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -775,12 +776,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -797,7 +798,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,17 +810,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10x11</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>215.00</t>
         </is>
       </c>
     </row>
@@ -831,7 +832,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -843,12 +844,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indoor Better 3rd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -860,51 +861,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10x11</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>220.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>217.00</t>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>270.00</t>
         </is>
       </c>
     </row>
@@ -916,29 +917,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>309.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>320.00</t>
         </is>
       </c>
     </row>
@@ -950,12 +951,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>324.00</t>
         </is>
       </c>
     </row>
@@ -967,29 +968,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>338.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>338.00</t>
+          <t>340.00</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,36 +1254,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>181.00</t>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>9x11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>293.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9x11</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1292,48 +1293,48 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>228.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>8x15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>228.00</t>
+          <t>273.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8x15</t>
+          <t>10x13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>233.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x13</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,7 +1344,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>259.00</t>
         </is>
       </c>
     </row>
@@ -1355,63 +1356,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>319.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>9x18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessPremiumClimate Controlled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>376.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9x18</t>
+          <t>10x17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Elevator AccessPremiumClimate Controlled</t>
+          <t>Drive Up Access</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>376.00</t>
+          <t>384.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x17</t>
+          <t>9x19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Drive Up Access</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>389.00</t>
         </is>
       </c>
     </row>
@@ -1423,29 +1424,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>Drive Up Access</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>389.00</t>
+          <t>449.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9x19</t>
+          <t>10x18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Drive Up Access</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>449.00</t>
+          <t>386.00</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1458,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>386.00</t>
+          <t>410.00</t>
         </is>
       </c>
     </row>
@@ -1474,29 +1475,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Drive Up Access</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>467.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x18</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Drive Up Access</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>467.00</t>
+          <t>429.00</t>
         </is>
       </c>
     </row>
@@ -1508,27 +1509,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>Drive Up Access</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>429.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10x20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Drive Up Access</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>514.00</t>
         </is>
@@ -1585,24 +1569,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5X10X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Drive-Up Non-Climate Control</t>
+          <t>Indoor First Floor Access Non-Climate Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>174.00</t>
+          <t>114.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8X10X8</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1612,14 +1596,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>234.00</t>
+          <t>174.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10X8X8</t>
+          <t>8X10X8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1629,31 +1613,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>234.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4X5X8</t>
+          <t>10X8X8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access Non-Climate Control</t>
+          <t>Drive-Up Non-Climate Control</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sold Out</t>
+          <t>257.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>4X5X8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1670,12 +1654,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5X4X8</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1704,12 +1688,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>5X15X8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+          <t>Indoor Heated First Floor Access</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1721,12 +1705,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5X10X8</t>
+          <t>5X4X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1738,12 +1722,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5X15X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access</t>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,19 +1919,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sold Out</t>
+          <t>1254.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11X19X8</t>
+          <t>10X32X8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Drive-Up A/C &amp; Heat</t>
+          <t>Drive-Up Non-Climate Control</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1959,7 +1943,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10X32X8</t>
+          <t>10X40X8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1976,12 +1960,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15X20X8</t>
+          <t>11X19X8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Drive-Up A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1993,12 +1977,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10X40X8</t>
+          <t>15X20X8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Drive-Up Non-Climate Control</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2078,7 +2062,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2088,14 +2072,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>169.00</t>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2105,82 +2089,82 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>169.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8X33</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seasonal Non-Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>179.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Non-Paved</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8X33</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>244.00</t>
+          <t>229.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10X28</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>244.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>10X28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2190,14 +2174,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sold Out</t>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8X17</t>
+          <t>10X18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2214,12 +2198,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8X21</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Non-Paved</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2231,12 +2215,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8X18</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2248,7 +2232,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10X18</t>
+          <t>10X33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2265,12 +2249,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10X33</t>
+          <t>10X38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2282,12 +2266,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2299,12 +2283,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Seasonal Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2316,12 +2300,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8X18</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2333,12 +2317,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2350,12 +2334,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8X31</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2367,12 +2351,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>8X31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2384,7 +2368,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10X38</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3313,4 +3297,265 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>unit_size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5X5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>96.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10X15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>320.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5X10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- 2 DOOR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>158.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10x5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1st Floor Standard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>220.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2nd Floor Standard</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2nd Floor Intermediate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>115.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2nd Floor Premium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>120.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2nd Floor Standard</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>165.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2nd Floor Intermediate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2nd Floor Premium</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>185.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10x5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2nd Floor Standard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>189.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10x5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2nd Floor Intermediate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10x5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2nd Floor Premium</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2nd Floor Premium</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>295.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-27_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,29 +866,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>219.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>220.00</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -917,19 +917,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -939,58 +939,58 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>309.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Indoor Best 1st floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>324.00</t>
+          <t>320.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>338.00</t>
+          <t>324.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>338.00</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1031,24 +1031,24 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>340.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1065,24 +1065,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Indoor Best 2nd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>345.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1099,29 +1099,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>350.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13.5x18.5</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1201 Bldg</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1133,49 +1133,66 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>13.5x18.5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indoor Best 1st floor</t>
+          <t>1201 Bldg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10x25</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Driveup New</t>
+          <t>Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>599.00</t>
+          <t>420.00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>10x25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>599.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>10x30</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Driveup New</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>749.00</t>
         </is>
@@ -1254,36 +1271,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>190.00</t>
+          <t>181.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9x11</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>9x11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1293,48 +1310,48 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>228.00</t>
+          <t>293.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>228.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10x13</t>
+          <t>8x15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>273.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1344,7 +1361,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>233.00</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1373,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>259.00</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1722,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5X4X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,12 +1739,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>5X8X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1739,7 +1756,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5X8X8</t>
+          <t>5X4X8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1977,12 +1994,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15X20X8</t>
+          <t>15X30X8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Drive-Up Non-Climate Control</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1994,7 +2011,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15X30X8</t>
+          <t>15X40X8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2011,7 +2028,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15X40X8</t>
+          <t>20X30X8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2028,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20X30X8</t>
+          <t>40X20X8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2045,12 +2062,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40X20X8</t>
+          <t>15X20X8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Drive-Up Non-Climate Control</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2249,12 +2266,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10X38</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2266,7 +2283,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8X17</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2283,12 +2300,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8X18</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2300,12 +2317,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8X21</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2317,12 +2334,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2334,12 +2351,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2351,12 +2368,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8X31</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2368,7 +2385,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>10X38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-29_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,24 +606,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>8x9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Bins Self Storage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>166.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,17 +640,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8x9</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bins Self Storage</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>171.00</t>
+          <t>170.00</t>
         </is>
       </c>
     </row>
@@ -2300,12 +2300,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8X23</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2317,12 +2317,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3345,77 +3345,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5X5</t>
+          <t>4X5X4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>44.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10X15</t>
+          <t>5X5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>96.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5X10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>- 2 DOOR</t>
-        </is>
-      </c>
+          <t>10X15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>158.00</t>
+          <t>320.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10x5</t>
+          <t>5X10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1st Floor Standard</t>
+          <t>- 2 DOOR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>158.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5x5</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2nd Floor Standard</t>
+          <t>1st Floor Standard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>110.00</t>
+          <t>220.00</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3423,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2nd Floor Intermediate</t>
+          <t>2nd Floor Standard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>110.00</t>
         </is>
       </c>
     </row>
@@ -3444,29 +3440,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2nd Floor Premium</t>
+          <t>2nd Floor Intermediate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>120.00</t>
+          <t>115.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2nd Floor Standard</t>
+          <t>2nd Floor Premium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>120.00</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3474,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2nd Floor Intermediate</t>
+          <t>2nd Floor Standard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>165.00</t>
         </is>
       </c>
     </row>
@@ -3495,29 +3491,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2nd Floor Premium</t>
+          <t>2nd Floor Intermediate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>185.00</t>
+          <t>175.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x5</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2nd Floor Standard</t>
+          <t>2nd Floor Premium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>189.00</t>
+          <t>185.00</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2nd Floor Intermediate</t>
+          <t>2nd Floor Standard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>200.00</t>
+          <t>189.00</t>
         </is>
       </c>
     </row>
@@ -3546,27 +3542,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2nd Floor Premium</t>
+          <t>2nd Floor Intermediate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>200.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10x5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2nd Floor Premium</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>210.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>10x10</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2nd Floor Premium</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>295.00</t>
         </is>

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-30_basalt_results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Sopris Self Storage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 StorQuest Self Storage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 StorageMart" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 All Hours Storage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Carbondale Mini Storage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Basalt Mini Storage" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -466,6 +476,14 @@
           <t>85.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -483,6 +501,14 @@
           <t>87.00</t>
         </is>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,6 +526,14 @@
           <t>95.00</t>
         </is>
       </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +551,14 @@
           <t>95.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -534,6 +576,14 @@
           <t>95.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -551,6 +601,14 @@
           <t>139.00</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -568,6 +626,14 @@
           <t>153.00</t>
         </is>
       </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,70 +643,102 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>153.00</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5x10</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>153.00</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8x9</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bins Self Storage</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>166.00</t>
+          <t>159.00</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>8x9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Bins Self Storage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>170.00</t>
+          <t>166.00</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -651,30 +749,46 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>170.00</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indoor Better 3rd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>173.00</t>
+          <t>170.00</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -685,40 +799,64 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>173.00</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15x5</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>173.00</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>15x5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indoor Best 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>175.00</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -738,21 +876,37 @@
           <t>176.00</t>
         </is>
       </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Best 3rd floor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>181.00</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
@@ -764,29 +918,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>212.00</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10x11</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>212.00</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -798,29 +968,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>212.00</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>215.00</t>
+          <t>212.00</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -832,19 +1018,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Indoor Better 3rd floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>215.00</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10x11</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -855,6 +1049,14 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>215.00</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
@@ -866,63 +1068,95 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Better 3rd floor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>219.00</t>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x10</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>219.00</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indoor Good 3rd floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>270.00</t>
+          <t>220.00</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -934,29 +1168,45 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>309.00</t>
+          <t>270.00</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Indoor Good 1st floor</t>
+          <t>Indoor Good 3rd floor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>270.00</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -968,46 +1218,70 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indoor Best 1st floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>324.00</t>
+          <t>278.00</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x16</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>338.00</t>
+          <t>312.00</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DriveUp Original Units</t>
+          <t>Indoor Good 1st floor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>320.00</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1293,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indoor Good 2nd floor</t>
+          <t>DriveUp Original Units</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>337.00</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1042,30 +1324,46 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>340.00</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indoor Better 2nd floor</t>
+          <t>Indoor Good 2nd floor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>340.00</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1076,30 +1374,46 @@
       <c r="C38" t="inlineStr">
         <is>
           <t>345.00</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indoor Best 2nd floor</t>
+          <t>Indoor Better 2nd floor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>345.00</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10x21</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1110,91 +1424,189 @@
       <c r="C40" t="inlineStr">
         <is>
           <t>350.00</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indoor Better 1st floor</t>
+          <t>Indoor Best 2nd floor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>350.00</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13.5x18.5</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1201 Bldg</t>
+          <t>Indoor Better 1st floor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>410.00</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>13.5x18.5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indoor Best 1st floor</t>
+          <t>1201 Bldg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>410.00</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10x25</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Driveup New</t>
+          <t>Indoor Best 1st floor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>599.00</t>
+          <t>420.00</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>12.5x22</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>550.00</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10x25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>599.00</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>10x30</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Driveup New</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>749.00</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1640,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1245,6 +1667,14 @@
           <t>88.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1262,6 +1692,14 @@
           <t>101.00</t>
         </is>
       </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1279,6 +1717,14 @@
           <t>181.00</t>
         </is>
       </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1296,6 +1742,14 @@
           <t>190.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1313,6 +1767,14 @@
           <t>293.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1330,11 +1792,19 @@
           <t>228.00</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8x15</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1344,31 +1814,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>239.00</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x13</t>
+          <t>8x15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>273.00</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10x15</t>
+          <t>10x13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1378,58 +1864,90 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>233.00</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9x18</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Elevator AccessPremiumClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>376.00</t>
+          <t>259.00</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x17</t>
+          <t>9x18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Drive Up Access</t>
+          <t>Elevator AccessPremiumClimate Controlled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>376.00</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9x19</t>
+          <t>10x17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>Drive Up Access</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>389.00</t>
+          <t>384.00</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1964,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>449.00</t>
+          <t>376.00</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10x18</t>
+          <t>9x19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1463,7 +1989,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>386.00</t>
+          <t>389.00</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1475,12 +2009,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1st FloorClimate Controlled</t>
+          <t>Elevator AccessClimate Controlled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>386.00</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1497,24 +2039,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>467.00</t>
+          <t>397.00</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x20</t>
+          <t>10x18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elevator AccessClimate Controlled</t>
+          <t>1st FloorClimate Controlled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>429.00</t>
+          <t>410.00</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1526,12 +2084,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Elevator AccessClimate Controlled</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>429.00</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Drive Up Access</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>514.00</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>441.00</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1546,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,6 +2156,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1582,38 +2183,62 @@
           <t>104.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access Non-Climate Control</t>
+          <t>Drive-Up Non-Climate Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>114.00</t>
+          <t>174.00</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5X10X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Drive-Up Non-Climate Control</t>
+          <t>Indoor Heated First Floor Access</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>174.00</t>
+          <t>197.00</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1633,6 +2258,14 @@
           <t>234.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1650,6 +2283,14 @@
           <t>257.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1667,6 +2308,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1684,6 +2333,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1701,6 +2358,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1718,38 +2383,62 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5X5X8</t>
+          <t>5X8X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5X8X8</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indoor First Floor Access A/C &amp; Heat</t>
+          <t>Indoor First Floor Access Non-Climate Control</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -1769,6 +2458,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1786,6 +2483,14 @@
           <t>259.00</t>
         </is>
       </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1803,6 +2508,14 @@
           <t>364.00</t>
         </is>
       </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1820,6 +2533,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1837,6 +2558,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1854,6 +2583,14 @@
           <t>449.00</t>
         </is>
       </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1871,6 +2608,14 @@
           <t>629.00</t>
         </is>
       </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1888,6 +2633,14 @@
           <t>902.00</t>
         </is>
       </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1905,6 +2658,14 @@
           <t>1019.00</t>
         </is>
       </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1922,6 +2683,14 @@
           <t>1132.00</t>
         </is>
       </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1939,6 +2708,14 @@
           <t>1254.00</t>
         </is>
       </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1956,6 +2733,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1973,6 +2758,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1990,6 +2783,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2007,6 +2808,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2024,6 +2833,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2041,6 +2858,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2058,6 +2883,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2075,6 +2908,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2092,6 +2933,14 @@
           <t>159.00</t>
         </is>
       </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2109,6 +2958,14 @@
           <t>169.00</t>
         </is>
       </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2126,6 +2983,14 @@
           <t>179.00</t>
         </is>
       </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2143,130 +3008,194 @@
           <t>199.00</t>
         </is>
       </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8X38</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Non-Paved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>209.00</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8X33</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Seasonal Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>244.00</t>
+          <t>228.00</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10X28</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>259.00</t>
+          <t>229.00</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10X18</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Seasonal Paved</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sold Out</t>
+          <t>244.00</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>10X28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Seasonal Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sold Out</t>
+          <t>259.00</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10X23</t>
+          <t>10X18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10X33</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Non-Paved</t>
+          <t>Paved</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8X17</t>
+          <t>10X33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2277,13 +3206,21 @@
       <c r="C43" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8X21</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2294,23 +3231,39 @@
       <c r="C44" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8X28</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paved</t>
+          <t>Non-Paved</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -2330,6 +3283,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2347,6 +3308,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2364,6 +3333,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2381,6 +3358,14 @@
           <t>Sold Out</t>
         </is>
       </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2396,6 +3381,14 @@
       <c r="C50" t="inlineStr">
         <is>
           <t>Sold Out</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>tier 0</t>
         </is>
       </c>
     </row>
@@ -2410,7 +3403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,6 +3422,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2446,6 +3449,14 @@
           <t>79.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2463,6 +3474,14 @@
           <t>99.00</t>
         </is>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2480,6 +3499,14 @@
           <t>117.00</t>
         </is>
       </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2497,6 +3524,14 @@
           <t>175.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2514,6 +3549,14 @@
           <t>190.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2531,6 +3574,14 @@
           <t>270.00</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2548,6 +3599,14 @@
           <t>375.00</t>
         </is>
       </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2565,6 +3624,14 @@
           <t>450.00</t>
         </is>
       </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2582,6 +3649,14 @@
           <t>500.00</t>
         </is>
       </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2599,6 +3674,14 @@
           <t>575.00</t>
         </is>
       </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2616,6 +3699,14 @@
           <t>695.00</t>
         </is>
       </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2633,6 +3724,14 @@
           <t>760.00</t>
         </is>
       </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2650,6 +3749,14 @@
           <t>750.00</t>
         </is>
       </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2667,6 +3774,14 @@
           <t>199.00</t>
         </is>
       </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2684,6 +3799,14 @@
           <t>299.00</t>
         </is>
       </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2701,6 +3824,14 @@
           <t>579.00</t>
         </is>
       </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2718,6 +3849,14 @@
           <t>650.00</t>
         </is>
       </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2735,6 +3874,14 @@
           <t>1,300.00</t>
         </is>
       </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2752,6 +3899,14 @@
           <t>1,737.00</t>
         </is>
       </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2769,6 +3924,14 @@
           <t>299.00</t>
         </is>
       </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2786,6 +3949,14 @@
           <t>579.00</t>
         </is>
       </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2803,6 +3974,14 @@
           <t>650.00</t>
         </is>
       </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2818,6 +3997,14 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>725.00</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
@@ -2832,7 +4019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,6 +4038,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2868,6 +4065,14 @@
           <t>365.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2885,6 +4090,14 @@
           <t>199.00</t>
         </is>
       </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2902,6 +4115,14 @@
           <t>199.00</t>
         </is>
       </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2919,6 +4140,14 @@
           <t>260.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2936,6 +4165,14 @@
           <t>240.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2953,6 +4190,14 @@
           <t>305.00</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2970,6 +4215,14 @@
           <t>365.00</t>
         </is>
       </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2987,6 +4240,14 @@
           <t>405.00</t>
         </is>
       </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3004,6 +4265,14 @@
           <t>475.00</t>
         </is>
       </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3021,6 +4290,14 @@
           <t>450.00</t>
         </is>
       </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3038,6 +4315,14 @@
           <t>385.00</t>
         </is>
       </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3055,6 +4340,14 @@
           <t>440.00</t>
         </is>
       </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3072,6 +4365,14 @@
           <t>570.00</t>
         </is>
       </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3089,6 +4390,14 @@
           <t>470.00</t>
         </is>
       </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3106,6 +4415,14 @@
           <t>440.00</t>
         </is>
       </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3123,6 +4440,14 @@
           <t>440.00</t>
         </is>
       </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3140,6 +4465,14 @@
           <t>530.00</t>
         </is>
       </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3157,6 +4490,14 @@
           <t>50.00</t>
         </is>
       </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3174,6 +4515,14 @@
           <t>80.00</t>
         </is>
       </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3191,6 +4540,14 @@
           <t>85.00</t>
         </is>
       </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3208,6 +4565,14 @@
           <t>90.00</t>
         </is>
       </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3225,6 +4590,14 @@
           <t>165.00</t>
         </is>
       </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3234,12 +4607,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Climate Control- Indoor Access</t>
+          <t>Drive up access</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>175.00</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>
@@ -3251,12 +4632,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Drive up access</t>
+          <t>Climate Control- Indoor Access</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>175.00</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tier 2</t>
         </is>
       </c>
     </row>
@@ -3276,6 +4665,14 @@
           <t>260.00</t>
         </is>
       </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3293,6 +4690,14 @@
           <t>110.00</t>
         </is>
       </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3308,6 +4713,14 @@
       <c r="C28" t="inlineStr">
         <is>
           <t>145.00</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tier 1</t>
         </is>
       </c>
     </row>
@@ -3322,7 +4735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,6 +4754,16 @@
           <t>price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>climate_controlled</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3354,6 +4777,14 @@
           <t>44.00</t>
         </is>
       </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3367,6 +4798,14 @@
           <t>96.00</t>
         </is>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3380,6 +4819,14 @@
           <t>320.00</t>
         </is>
       </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3397,6 +4844,14 @@
           <t>158.00</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tier 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3414,6 +4869,14 @@
           <t>220.00</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3431,6 +4894,14 @@
           <t>110.00</t>
         </is>
       </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3448,6 +4919,14 @@
           <t>115.00</t>
         </is>
       </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3465,6 +4944,14 @@
           <t>120.00</t>
         </is>
       </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3482,6 +4969,14 @@
           <t>165.00</t>
         </is>
       </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3499,6 +4994,14 @@
           <t>175.00</t>
         </is>
       </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3516,6 +5019,14 @@
           <t>185.00</t>
         </is>
       </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3533,6 +5044,14 @@
           <t>189.00</t>
         </is>
       </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tier 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3550,6 +5069,14 @@
           <t>200.00</t>
         </is>
       </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3567,6 +5094,14 @@
           <t>210.00</t>
         </is>
       </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3582,6 +5117,14 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>295.00</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tier 3</t>
         </is>
       </c>
     </row>

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Sopris Self Storage" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 StorQuest Self Storage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 StorageMart" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 All Hours Storage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Carbondale Mini Storage" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-01 Basalt Mini Storage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 Sopris Self Storage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 StorQuest Self Storage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 StorageMart" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 All Hours Storage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 Carbondale Mini Storage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-02 Basalt Mini Storage" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>88.00</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -2245,7 +2245,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8X10X8</t>
+          <t>10X8X8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10X8X8</t>
+          <t>8X10X8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>257.00</t>
+          <t>234.00</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -4810,13 +4810,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10X15</t>
+          <t>5X10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>155.00</t>
         </is>
       </c>
       <c r="D4" t="b">

--- a/storage_results.xlsx
+++ b/storage_results.xlsx
@@ -7,19 +7,19 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="07-13 Sopris Self Storage" sheetId="1" r:id="rId1"/>
-    <sheet name="07-13 StorQuest Self Storage" sheetId="2" r:id="rId2"/>
-    <sheet name="07-13 StorageMart" sheetId="3" r:id="rId3"/>
-    <sheet name="07-13 All Hours Storage" sheetId="4" r:id="rId4"/>
-    <sheet name="07-13 Carbondale Mini Storage" sheetId="5" r:id="rId5"/>
-    <sheet name="07-13 Basalt Mini Storage" sheetId="6" r:id="rId6"/>
+    <sheet name="08-13 Sopris Self Storage" sheetId="1" r:id="rId1"/>
+    <sheet name="08-13 StorQuest Self Storage" sheetId="2" r:id="rId2"/>
+    <sheet name="08-13 StorageMart" sheetId="3" r:id="rId3"/>
+    <sheet name="08-13 All Hours Storage" sheetId="4" r:id="rId4"/>
+    <sheet name="08-13 Carbondale Mini Storage" sheetId="5" r:id="rId5"/>
+    <sheet name="08-13 Basalt Mini Storage" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="235">
   <si>
     <t>unit_size</t>
   </si>
@@ -36,15 +36,18 @@
     <t>tier</t>
   </si>
   <si>
+    <t>5x3.5</t>
+  </si>
+  <si>
     <t>5x5</t>
   </si>
   <si>
+    <t>10x5</t>
+  </si>
+  <si>
     <t>5x10</t>
   </si>
   <si>
-    <t>10x5</t>
-  </si>
-  <si>
     <t>8x9</t>
   </si>
   <si>
@@ -54,9 +57,6 @@
     <t>10x21</t>
   </si>
   <si>
-    <t>15x5</t>
-  </si>
-  <si>
     <t>5x15</t>
   </si>
   <si>
@@ -81,694 +81,625 @@
     <t>10x25</t>
   </si>
   <si>
+    <t>Indoor Good 3rd floor</t>
+  </si>
+  <si>
+    <t>Driveup Hallway</t>
+  </si>
+  <si>
+    <t>DriveUp Original Units</t>
+  </si>
+  <si>
+    <t>Indoor Good 2nd floor</t>
+  </si>
+  <si>
+    <t>Indoor Good 1st floor</t>
+  </si>
+  <si>
+    <t>Bins Self Storage</t>
+  </si>
+  <si>
+    <t>Indoor Better 3rd floor</t>
+  </si>
+  <si>
+    <t>Indoor Best 3rd floor</t>
+  </si>
+  <si>
+    <t>Indoor Better 2nd floor</t>
+  </si>
+  <si>
+    <t>Indoor Better 1st floor</t>
+  </si>
+  <si>
+    <t>Indoor Best 2nd floor</t>
+  </si>
+  <si>
+    <t>1201 Bldg</t>
+  </si>
+  <si>
+    <t>Indoor Best 1st floor</t>
+  </si>
+  <si>
+    <t>Driveup New</t>
+  </si>
+  <si>
+    <t>86.00</t>
+  </si>
+  <si>
+    <t>88.00</t>
+  </si>
+  <si>
+    <t>98.00</t>
+  </si>
+  <si>
+    <t>153.00</t>
+  </si>
+  <si>
+    <t>166.00</t>
+  </si>
+  <si>
+    <t>170.00</t>
+  </si>
+  <si>
+    <t>171.00</t>
+  </si>
+  <si>
+    <t>173.00</t>
+  </si>
+  <si>
+    <t>175.00</t>
+  </si>
+  <si>
+    <t>178.00</t>
+  </si>
+  <si>
+    <t>212.00</t>
+  </si>
+  <si>
+    <t>215.00</t>
+  </si>
+  <si>
+    <t>219.00</t>
+  </si>
+  <si>
+    <t>270.00</t>
+  </si>
+  <si>
+    <t>276.00</t>
+  </si>
+  <si>
+    <t>278.00</t>
+  </si>
+  <si>
+    <t>320.00</t>
+  </si>
+  <si>
+    <t>328.00</t>
+  </si>
+  <si>
+    <t>340.00</t>
+  </si>
+  <si>
+    <t>345.00</t>
+  </si>
+  <si>
+    <t>350.00</t>
+  </si>
+  <si>
+    <t>410.00</t>
+  </si>
+  <si>
+    <t>420.00</t>
+  </si>
+  <si>
+    <t>550.00</t>
+  </si>
+  <si>
+    <t>599.00</t>
+  </si>
+  <si>
+    <t>tier 1</t>
+  </si>
+  <si>
+    <t>tier 0</t>
+  </si>
+  <si>
+    <t>tier 2</t>
+  </si>
+  <si>
+    <t>tier 3</t>
+  </si>
+  <si>
+    <t>9x11</t>
+  </si>
+  <si>
+    <t>8x15</t>
+  </si>
+  <si>
+    <t>10x13</t>
+  </si>
+  <si>
+    <t>9x18</t>
+  </si>
+  <si>
+    <t>10x17</t>
+  </si>
+  <si>
+    <t>9x19</t>
+  </si>
+  <si>
+    <t>10x18</t>
+  </si>
+  <si>
+    <t>Elevator AccessClimate Controlled</t>
+  </si>
+  <si>
+    <t>1st FloorClimate Controlled</t>
+  </si>
+  <si>
+    <t>Elevator AccessPremiumClimate Controlled</t>
+  </si>
+  <si>
+    <t>Drive Up Access</t>
+  </si>
+  <si>
+    <t>103.00</t>
+  </si>
+  <si>
+    <t>127.00</t>
+  </si>
+  <si>
+    <t>244.00</t>
+  </si>
+  <si>
+    <t>252.00</t>
+  </si>
+  <si>
+    <t>246.00</t>
+  </si>
+  <si>
+    <t>358.00</t>
+  </si>
+  <si>
+    <t>428.00</t>
+  </si>
+  <si>
+    <t>176.00</t>
+  </si>
+  <si>
+    <t>351.00</t>
+  </si>
+  <si>
+    <t>486.00</t>
+  </si>
+  <si>
+    <t>436.00</t>
+  </si>
+  <si>
+    <t>309.00</t>
+  </si>
+  <si>
+    <t>449.00</t>
+  </si>
+  <si>
+    <t>337.00</t>
+  </si>
+  <si>
+    <t>402.00</t>
+  </si>
+  <si>
+    <t>361.00</t>
+  </si>
+  <si>
+    <t>491.00</t>
+  </si>
+  <si>
+    <t>5X5X8</t>
+  </si>
+  <si>
+    <t>5X10X8</t>
+  </si>
+  <si>
+    <t>8X10X8</t>
+  </si>
+  <si>
+    <t>10X8X8</t>
+  </si>
+  <si>
+    <t>4X5X8</t>
+  </si>
+  <si>
+    <t>5X15X8</t>
+  </si>
+  <si>
+    <t>5X4X8</t>
+  </si>
+  <si>
+    <t>5X8X8</t>
+  </si>
+  <si>
+    <t>10X10X8</t>
+  </si>
+  <si>
+    <t>10X15X8</t>
+  </si>
+  <si>
+    <t>10X11X8</t>
+  </si>
+  <si>
+    <t>10X14X8</t>
+  </si>
+  <si>
+    <t>10X20X8</t>
+  </si>
+  <si>
+    <t>10X25X8</t>
+  </si>
+  <si>
+    <t>10X30X8</t>
+  </si>
+  <si>
+    <t>15X20X8</t>
+  </si>
+  <si>
+    <t>20X20X8</t>
+  </si>
+  <si>
+    <t>20X25X8</t>
+  </si>
+  <si>
+    <t>15X30X8</t>
+  </si>
+  <si>
+    <t>10X32X8</t>
+  </si>
+  <si>
+    <t>10X40X8</t>
+  </si>
+  <si>
+    <t>11X19X8</t>
+  </si>
+  <si>
+    <t>15X40X8</t>
+  </si>
+  <si>
+    <t>20X30X8</t>
+  </si>
+  <si>
+    <t>30X20X8</t>
+  </si>
+  <si>
+    <t>40X20X8</t>
+  </si>
+  <si>
+    <t>Drive-Up Non-Climate Control</t>
+  </si>
+  <si>
+    <t>Indoor Heated First Floor Access</t>
+  </si>
+  <si>
+    <t>Indoor First Floor Access Non-Climate Control</t>
+  </si>
+  <si>
+    <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+  </si>
+  <si>
+    <t>Indoor First Floor Access A/C &amp; Heat</t>
+  </si>
+  <si>
+    <t>Heated Drive-Up</t>
+  </si>
+  <si>
+    <t>Drive-Up A/C &amp; Heat</t>
+  </si>
+  <si>
+    <t>99.00</t>
+  </si>
+  <si>
+    <t>Sold Out</t>
+  </si>
+  <si>
+    <t>263.00</t>
+  </si>
+  <si>
+    <t>902.00</t>
+  </si>
+  <si>
+    <t>5x5x4</t>
+  </si>
+  <si>
+    <t>5x5x8</t>
+  </si>
+  <si>
     <t>10x30</t>
   </si>
   <si>
-    <t>Driveup Hallway</t>
-  </si>
-  <si>
-    <t>Indoor Better 2nd floor</t>
-  </si>
-  <si>
-    <t>Indoor Better 3rd floor</t>
-  </si>
-  <si>
-    <t>Indoor Good 3rd floor</t>
-  </si>
-  <si>
-    <t>DriveUp Original Units</t>
-  </si>
-  <si>
-    <t>Indoor Best 2nd floor</t>
-  </si>
-  <si>
-    <t>Indoor Good 2nd floor</t>
-  </si>
-  <si>
-    <t>Bins Self Storage</t>
-  </si>
-  <si>
-    <t>Indoor Best 3rd floor</t>
-  </si>
-  <si>
-    <t>Indoor Good 1st floor</t>
-  </si>
-  <si>
-    <t>Indoor Better 1st floor</t>
-  </si>
-  <si>
-    <t>1201 Bldg</t>
-  </si>
-  <si>
-    <t>Indoor Best 1st floor</t>
-  </si>
-  <si>
-    <t>Driveup New</t>
-  </si>
-  <si>
-    <t>89.00</t>
-  </si>
-  <si>
-    <t>95.00</t>
+    <t>15x30</t>
+  </si>
+  <si>
+    <t>20x20</t>
+  </si>
+  <si>
+    <t>19x9</t>
+  </si>
+  <si>
+    <t>10x10x10</t>
+  </si>
+  <si>
+    <t>10x20x10</t>
+  </si>
+  <si>
+    <t>10x30x10</t>
+  </si>
+  <si>
+    <t>10x40x10</t>
+  </si>
+  <si>
+    <t>20x40x10</t>
+  </si>
+  <si>
+    <t>30x10</t>
+  </si>
+  <si>
+    <t>20x20x10</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>5X5CC</t>
+  </si>
+  <si>
+    <t>5X10CC</t>
+  </si>
+  <si>
+    <t>10X10CC</t>
+  </si>
+  <si>
+    <t>Heated 10X20CC</t>
+  </si>
+  <si>
+    <t>Paved Outside Parking</t>
+  </si>
+  <si>
+    <t>Ultimate 10 x 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate </t>
+  </si>
+  <si>
+    <t>Ultimate 10 x 30</t>
+  </si>
+  <si>
+    <t>Ultimate 10 x 40</t>
+  </si>
+  <si>
+    <t>Ultimate 20 x 40</t>
+  </si>
+  <si>
+    <t>Ultimate 10 x 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate 20 x 20 </t>
+  </si>
+  <si>
+    <t>79.00</t>
+  </si>
+  <si>
+    <t>117.00</t>
+  </si>
+  <si>
+    <t>190.00</t>
+  </si>
+  <si>
+    <t>375.00</t>
+  </si>
+  <si>
+    <t>450.00</t>
+  </si>
+  <si>
+    <t>500.00</t>
+  </si>
+  <si>
+    <t>575.00</t>
+  </si>
+  <si>
+    <t>695.00</t>
+  </si>
+  <si>
+    <t>760.00</t>
+  </si>
+  <si>
+    <t>750.00</t>
+  </si>
+  <si>
+    <t>199.00</t>
+  </si>
+  <si>
+    <t>299.00</t>
+  </si>
+  <si>
+    <t>579.00</t>
+  </si>
+  <si>
+    <t>650.00</t>
+  </si>
+  <si>
+    <t>1,300.00</t>
+  </si>
+  <si>
+    <t>1,737.00</t>
+  </si>
+  <si>
+    <t>725.00</t>
+  </si>
+  <si>
+    <t>10X20</t>
+  </si>
+  <si>
+    <t>12x20</t>
+  </si>
+  <si>
+    <t>12x30</t>
+  </si>
+  <si>
+    <t>12x35</t>
+  </si>
+  <si>
+    <t>13x25</t>
+  </si>
+  <si>
+    <t>15x20</t>
+  </si>
+  <si>
+    <t>15x25</t>
+  </si>
+  <si>
+    <t>3X2.7</t>
+  </si>
+  <si>
+    <t>5X4X4</t>
+  </si>
+  <si>
+    <t>5X5X4</t>
+  </si>
+  <si>
+    <t>7x25</t>
+  </si>
+  <si>
+    <t>Outdoor</t>
+  </si>
+  <si>
+    <t>Double Unit/ Drive up access</t>
+  </si>
+  <si>
+    <t>Drive up access</t>
+  </si>
+  <si>
+    <t>Non Climate Control- Indoor Access</t>
+  </si>
+  <si>
+    <t>Climate Control- Indoor access</t>
+  </si>
+  <si>
+    <t>Climate Control - Indoor access</t>
+  </si>
+  <si>
+    <t>Climate Control</t>
+  </si>
+  <si>
+    <t>(CC)</t>
+  </si>
+  <si>
+    <t>None listed</t>
+  </si>
+  <si>
+    <t>Indoor Lockers</t>
+  </si>
+  <si>
+    <t>Climate Control- Indoor Access</t>
+  </si>
+  <si>
+    <t>Parking</t>
+  </si>
+  <si>
+    <t>365.00</t>
+  </si>
+  <si>
+    <t>260.00</t>
+  </si>
+  <si>
+    <t>240.00</t>
+  </si>
+  <si>
+    <t>305.00</t>
+  </si>
+  <si>
+    <t>405.00</t>
+  </si>
+  <si>
+    <t>475.00</t>
+  </si>
+  <si>
+    <t>385.00</t>
+  </si>
+  <si>
+    <t>440.00</t>
+  </si>
+  <si>
+    <t>570.00</t>
+  </si>
+  <si>
+    <t>470.00</t>
+  </si>
+  <si>
+    <t>530.00</t>
+  </si>
+  <si>
+    <t>50.00</t>
+  </si>
+  <si>
+    <t>80.00</t>
+  </si>
+  <si>
+    <t>85.00</t>
+  </si>
+  <si>
+    <t>90.00</t>
+  </si>
+  <si>
+    <t>165.00</t>
+  </si>
+  <si>
+    <t>110.00</t>
   </si>
   <si>
     <t>145.00</t>
   </si>
   <si>
-    <t>153.00</t>
+    <t>4X5X4</t>
+  </si>
+  <si>
+    <t>5X5</t>
+  </si>
+  <si>
+    <t>5X10</t>
+  </si>
+  <si>
+    <t>- 2 DOOR</t>
+  </si>
+  <si>
+    <t>1st Floor Standard</t>
+  </si>
+  <si>
+    <t>1st Floor Premium</t>
+  </si>
+  <si>
+    <t>2nd Floor Standard</t>
+  </si>
+  <si>
+    <t>2nd Floor Intermediate</t>
+  </si>
+  <si>
+    <t>2nd Floor Premium</t>
+  </si>
+  <si>
+    <t>44.00</t>
+  </si>
+  <si>
+    <t>96.00</t>
+  </si>
+  <si>
+    <t>155.00</t>
   </si>
   <si>
     <t>158.00</t>
   </si>
   <si>
-    <t>166.00</t>
-  </si>
-  <si>
-    <t>170.00</t>
-  </si>
-  <si>
-    <t>173.00</t>
-  </si>
-  <si>
-    <t>175.00</t>
-  </si>
-  <si>
-    <t>176.00</t>
-  </si>
-  <si>
-    <t>181.00</t>
-  </si>
-  <si>
-    <t>212.00</t>
-  </si>
-  <si>
-    <t>215.00</t>
-  </si>
-  <si>
-    <t>217.00</t>
-  </si>
-  <si>
-    <t>219.00</t>
-  </si>
-  <si>
-    <t>270.00</t>
-  </si>
-  <si>
-    <t>278.00</t>
-  </si>
-  <si>
-    <t>320.00</t>
-  </si>
-  <si>
-    <t>338.00</t>
-  </si>
-  <si>
-    <t>340.00</t>
-  </si>
-  <si>
-    <t>345.00</t>
-  </si>
-  <si>
-    <t>350.00</t>
-  </si>
-  <si>
-    <t>410.00</t>
-  </si>
-  <si>
-    <t>420.00</t>
-  </si>
-  <si>
-    <t>550.00</t>
-  </si>
-  <si>
-    <t>599.00</t>
-  </si>
-  <si>
-    <t>749.00</t>
-  </si>
-  <si>
-    <t>tier 0</t>
-  </si>
-  <si>
-    <t>tier 2</t>
-  </si>
-  <si>
-    <t>tier 1</t>
-  </si>
-  <si>
-    <t>tier 3</t>
-  </si>
-  <si>
-    <t>9x11</t>
-  </si>
-  <si>
-    <t>8x15</t>
-  </si>
-  <si>
-    <t>10x13</t>
-  </si>
-  <si>
-    <t>9x18</t>
-  </si>
-  <si>
-    <t>9x19</t>
-  </si>
-  <si>
-    <t>10x18</t>
-  </si>
-  <si>
-    <t>Elevator AccessClimate Controlled</t>
-  </si>
-  <si>
-    <t>1st FloorClimate Controlled</t>
-  </si>
-  <si>
-    <t>Elevator AccessPremiumClimate Controlled</t>
-  </si>
-  <si>
-    <t>Drive Up Access</t>
-  </si>
-  <si>
-    <t>88.00</t>
-  </si>
-  <si>
-    <t>101.00</t>
-  </si>
-  <si>
-    <t>190.00</t>
-  </si>
-  <si>
-    <t>293.00</t>
-  </si>
-  <si>
-    <t>228.00</t>
-  </si>
-  <si>
-    <t>239.00</t>
-  </si>
-  <si>
-    <t>273.00</t>
-  </si>
-  <si>
-    <t>233.00</t>
-  </si>
-  <si>
-    <t>259.00</t>
-  </si>
-  <si>
-    <t>319.00</t>
-  </si>
-  <si>
-    <t>376.00</t>
-  </si>
-  <si>
-    <t>389.00</t>
-  </si>
-  <si>
-    <t>386.00</t>
-  </si>
-  <si>
-    <t>397.00</t>
-  </si>
-  <si>
-    <t>429.00</t>
-  </si>
-  <si>
-    <t>441.00</t>
-  </si>
-  <si>
-    <t>5X5X8</t>
-  </si>
-  <si>
-    <t>5X10X8</t>
-  </si>
-  <si>
-    <t>10X8X8</t>
-  </si>
-  <si>
-    <t>8X10X8</t>
-  </si>
-  <si>
-    <t>4X5X8</t>
-  </si>
-  <si>
-    <t>5X4X8</t>
-  </si>
-  <si>
-    <t>5X8X8</t>
-  </si>
-  <si>
-    <t>5X15X8</t>
-  </si>
-  <si>
-    <t>10X10X8</t>
-  </si>
-  <si>
-    <t>10X15X8</t>
-  </si>
-  <si>
-    <t>10X11X8</t>
-  </si>
-  <si>
-    <t>10X14X8</t>
-  </si>
-  <si>
-    <t>10X20X8</t>
-  </si>
-  <si>
-    <t>10X25X8</t>
-  </si>
-  <si>
-    <t>10X30X8</t>
-  </si>
-  <si>
-    <t>20X20X8</t>
-  </si>
-  <si>
-    <t>30X20X8</t>
-  </si>
-  <si>
-    <t>11X19X8</t>
-  </si>
-  <si>
-    <t>10X32X8</t>
-  </si>
-  <si>
-    <t>15X20X8</t>
-  </si>
-  <si>
-    <t>10X40X8</t>
-  </si>
-  <si>
-    <t>15X30X8</t>
-  </si>
-  <si>
-    <t>20X25X8</t>
-  </si>
-  <si>
-    <t>15X40X8</t>
-  </si>
-  <si>
-    <t>20X30X8</t>
-  </si>
-  <si>
-    <t>40X20X8</t>
-  </si>
-  <si>
-    <t>8X28</t>
-  </si>
-  <si>
-    <t>10X18</t>
-  </si>
-  <si>
-    <t>8X38</t>
-  </si>
-  <si>
-    <t>8X33</t>
-  </si>
-  <si>
-    <t>8X18</t>
-  </si>
-  <si>
-    <t>8X23</t>
-  </si>
-  <si>
-    <t>8X17</t>
-  </si>
-  <si>
-    <t>8X21</t>
-  </si>
-  <si>
-    <t>10X23</t>
-  </si>
-  <si>
-    <t>8X31</t>
-  </si>
-  <si>
-    <t>10X28</t>
-  </si>
-  <si>
-    <t>10X33</t>
-  </si>
-  <si>
-    <t>10X38</t>
-  </si>
-  <si>
-    <t>Drive-Up Non-Climate Control</t>
-  </si>
-  <si>
-    <t>Indoor Heated First Floor Access</t>
-  </si>
-  <si>
-    <t>Indoor First Floor Access Non-Climate Control</t>
-  </si>
-  <si>
-    <t>Indoor First Floor Access A/C &amp; Heat</t>
-  </si>
-  <si>
-    <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
-  </si>
-  <si>
-    <t>Heated Drive-Up</t>
-  </si>
-  <si>
-    <t>Drive-Up A/C &amp; Heat</t>
-  </si>
-  <si>
-    <t>Non-Paved</t>
-  </si>
-  <si>
-    <t>Seasonal Paved</t>
-  </si>
-  <si>
-    <t>Seasonal Non-Paved</t>
-  </si>
-  <si>
-    <t>Paved</t>
-  </si>
-  <si>
-    <t>99.00</t>
-  </si>
-  <si>
-    <t>174.00</t>
-  </si>
-  <si>
-    <t>197.00</t>
-  </si>
-  <si>
-    <t>234.00</t>
-  </si>
-  <si>
-    <t>257.00</t>
-  </si>
-  <si>
-    <t>Sold Out</t>
-  </si>
-  <si>
-    <t>449.00</t>
-  </si>
-  <si>
-    <t>629.00</t>
-  </si>
-  <si>
-    <t>902.00</t>
-  </si>
-  <si>
-    <t>1101.00</t>
-  </si>
-  <si>
-    <t>1254.00</t>
-  </si>
-  <si>
-    <t>179.00</t>
-  </si>
-  <si>
-    <t>194.00</t>
-  </si>
-  <si>
-    <t>229.00</t>
-  </si>
-  <si>
-    <t>244.00</t>
-  </si>
-  <si>
-    <t>5x5x4</t>
-  </si>
-  <si>
-    <t>5x5x8</t>
-  </si>
-  <si>
-    <t>15x30</t>
-  </si>
-  <si>
-    <t>20x20</t>
-  </si>
-  <si>
-    <t>19x9</t>
-  </si>
-  <si>
-    <t>10x10x10</t>
-  </si>
-  <si>
-    <t>10x20x10</t>
-  </si>
-  <si>
-    <t>10x30x10</t>
-  </si>
-  <si>
-    <t>10x40x10</t>
-  </si>
-  <si>
-    <t>20x40x10</t>
-  </si>
-  <si>
-    <t>30x10</t>
-  </si>
-  <si>
-    <t>20x20x10</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>5X5CC</t>
-  </si>
-  <si>
-    <t>5X10CC</t>
-  </si>
-  <si>
-    <t>10X10CC</t>
-  </si>
-  <si>
-    <t>Heated 10X20CC</t>
-  </si>
-  <si>
-    <t>Paved Outside Parking</t>
-  </si>
-  <si>
-    <t>Ultimate 10 x 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimate </t>
-  </si>
-  <si>
-    <t>Ultimate 10 x 30</t>
-  </si>
-  <si>
-    <t>Ultimate 10 x 40</t>
-  </si>
-  <si>
-    <t>Ultimate 20 x 40</t>
-  </si>
-  <si>
-    <t>Ultimate 10 x 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimate 20 x 20 </t>
-  </si>
-  <si>
-    <t>79.00</t>
-  </si>
-  <si>
-    <t>117.00</t>
-  </si>
-  <si>
-    <t>375.00</t>
-  </si>
-  <si>
-    <t>450.00</t>
-  </si>
-  <si>
-    <t>500.00</t>
-  </si>
-  <si>
-    <t>575.00</t>
-  </si>
-  <si>
-    <t>695.00</t>
-  </si>
-  <si>
-    <t>760.00</t>
-  </si>
-  <si>
-    <t>750.00</t>
-  </si>
-  <si>
-    <t>199.00</t>
-  </si>
-  <si>
-    <t>299.00</t>
-  </si>
-  <si>
-    <t>579.00</t>
-  </si>
-  <si>
-    <t>650.00</t>
-  </si>
-  <si>
-    <t>1,300.00</t>
-  </si>
-  <si>
-    <t>1,737.00</t>
-  </si>
-  <si>
-    <t>725.00</t>
-  </si>
-  <si>
-    <t>10X20</t>
-  </si>
-  <si>
-    <t>12x20</t>
-  </si>
-  <si>
-    <t>12x30</t>
-  </si>
-  <si>
-    <t>12x35</t>
-  </si>
-  <si>
-    <t>13x25</t>
-  </si>
-  <si>
-    <t>15x20</t>
-  </si>
-  <si>
-    <t>15x25</t>
-  </si>
-  <si>
-    <t>3X2.7</t>
-  </si>
-  <si>
-    <t>5X4X4</t>
-  </si>
-  <si>
-    <t>5X5X4</t>
-  </si>
-  <si>
-    <t>7x25</t>
-  </si>
-  <si>
-    <t>Outdoor</t>
-  </si>
-  <si>
-    <t>Double Unit/ Drive up access</t>
-  </si>
-  <si>
-    <t>Drive up access</t>
-  </si>
-  <si>
-    <t>Non Climate Control- Indoor Access</t>
-  </si>
-  <si>
-    <t>Climate Control- Indoor access</t>
-  </si>
-  <si>
-    <t>Climate Control - Indoor access</t>
-  </si>
-  <si>
-    <t>Climate Control</t>
-  </si>
-  <si>
-    <t>(CC)</t>
-  </si>
-  <si>
-    <t>None listed</t>
-  </si>
-  <si>
-    <t>Indoor Lockers</t>
-  </si>
-  <si>
-    <t>Climate Control- Indoor Access</t>
-  </si>
-  <si>
-    <t>Parking</t>
-  </si>
-  <si>
-    <t>365.00</t>
-  </si>
-  <si>
-    <t>260.00</t>
-  </si>
-  <si>
-    <t>240.00</t>
-  </si>
-  <si>
-    <t>305.00</t>
-  </si>
-  <si>
-    <t>405.00</t>
-  </si>
-  <si>
-    <t>475.00</t>
-  </si>
-  <si>
-    <t>385.00</t>
-  </si>
-  <si>
-    <t>440.00</t>
-  </si>
-  <si>
-    <t>570.00</t>
-  </si>
-  <si>
-    <t>470.00</t>
-  </si>
-  <si>
-    <t>530.00</t>
-  </si>
-  <si>
-    <t>50.00</t>
-  </si>
-  <si>
-    <t>80.00</t>
-  </si>
-  <si>
-    <t>85.00</t>
-  </si>
-  <si>
-    <t>90.00</t>
-  </si>
-  <si>
-    <t>165.00</t>
-  </si>
-  <si>
-    <t>110.00</t>
-  </si>
-  <si>
-    <t>5X5</t>
-  </si>
-  <si>
-    <t>5X10</t>
-  </si>
-  <si>
-    <t>10X10</t>
-  </si>
-  <si>
-    <t>- 2 DOOR</t>
-  </si>
-  <si>
-    <t>1st Floor Standard</t>
-  </si>
-  <si>
-    <t>1st Floor Premium</t>
-  </si>
-  <si>
-    <t>2nd Floor Standard</t>
-  </si>
-  <si>
-    <t>2nd Floor Intermediate</t>
-  </si>
-  <si>
-    <t>2nd Floor Premium</t>
-  </si>
-  <si>
-    <t>96.00</t>
-  </si>
-  <si>
-    <t>155.00</t>
-  </si>
-  <si>
-    <t>225.00</t>
+    <t>132.00</t>
+  </si>
+  <si>
+    <t>138.00</t>
   </si>
   <si>
     <t>220.00</t>
@@ -790,9 +721,6 @@
   </si>
   <si>
     <t>210.00</t>
-  </si>
-  <si>
-    <t>275.00</t>
   </si>
   <si>
     <t>295.00</t>
@@ -1178,58 +1106,58 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
@@ -1238,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1246,16 +1174,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1263,16 +1191,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1280,101 +1208,101 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1382,16 +1310,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1399,30 +1327,30 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -1430,36 +1358,36 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1467,33 +1395,33 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1501,33 +1429,33 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1535,33 +1463,33 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1569,16 +1497,16 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1586,16 +1514,16 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1603,16 +1531,16 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1620,16 +1548,16 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1640,81 +1568,81 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1722,33 +1650,33 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1756,33 +1684,33 @@
         <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D37" t="b">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1790,118 +1718,118 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D38" t="b">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1911,7 +1839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1933,87 +1861,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2021,67 +1949,67 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2089,27 +2017,27 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -2120,61 +2048,61 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
         <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>86</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
         <v>88</v>
@@ -2183,15 +2111,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
         <v>89</v>
@@ -2200,58 +2128,24 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2283,104 +2177,104 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2388,730 +2282,407 @@
         <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="D21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
         <v>117</v>
       </c>
-      <c r="B31" t="s">
-        <v>131</v>
-      </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" t="s">
-        <v>139</v>
-      </c>
-      <c r="C38" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B40" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" t="s">
-        <v>147</v>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" t="s">
-        <v>147</v>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" t="s">
-        <v>138</v>
-      </c>
-      <c r="C46" t="s">
-        <v>147</v>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" t="s">
-        <v>139</v>
-      </c>
-      <c r="C48" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C49" t="s">
-        <v>147</v>
-      </c>
-      <c r="D49" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B50" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" t="s">
-        <v>147</v>
-      </c>
-      <c r="D50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3143,87 +2714,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3231,16 +2802,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3248,50 +2819,50 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3299,237 +2870,237 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
         <v>167</v>
       </c>
-      <c r="B23" t="s">
-        <v>177</v>
-      </c>
-      <c r="C23" t="s">
-        <v>194</v>
-      </c>
       <c r="D23" t="b">
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3561,19 +3132,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3581,16 +3152,16 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3598,16 +3169,16 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3615,16 +3186,16 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3632,16 +3203,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3649,33 +3220,33 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3683,339 +3254,339 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" t="s">
         <v>204</v>
       </c>
-      <c r="B18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" t="s">
-        <v>231</v>
-      </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" t="s">
         <v>205</v>
       </c>
-      <c r="B19" t="s">
-        <v>217</v>
-      </c>
-      <c r="C19" t="s">
-        <v>232</v>
-      </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" t="s">
         <v>206</v>
       </c>
-      <c r="B20" t="s">
-        <v>218</v>
-      </c>
-      <c r="C20" t="s">
-        <v>233</v>
-      </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" t="s">
         <v>207</v>
       </c>
-      <c r="B21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C21" t="s">
-        <v>234</v>
-      </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C22" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C23" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="B26" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4025,7 +3596,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4047,61 +3618,61 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>224</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4109,33 +3680,33 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4143,118 +3714,118 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4262,16 +3833,16 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4279,67 +3850,33 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C18" t="s">
-        <v>257</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
